--- a/etf_holdings/2026-09-29_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-09-29_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2475</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.93%5285</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.93%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5285</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.16%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.16%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1185</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.6%5050</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5050</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.45%3555</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.45%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3555</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.96%6920</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.96%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6920</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.22%580</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>580</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.53%1910</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1910</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.65%5415</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.65%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5415</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.75%154</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>154</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.26%1895</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1895</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.48%1240</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1240</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.48%2115</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2115</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.87%699</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.87%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>699</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%2340</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2340</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3599,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3660,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3721,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3782,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3843,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3904,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3965,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4026,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4087,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4148,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4209,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4270,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4331,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4392,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4453,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4514,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4575,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4636,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4697,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4758,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4819,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4880,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4941,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5002,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5063,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5124,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5185,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5246,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5307,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5368,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5429,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5490,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5551,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5612,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5673,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5734,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5795,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5856,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5917,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5978,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6039,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6100,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6161,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6222,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6283,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6344,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6405,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6466,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6527,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6588,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6649,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6710,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6771,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6832,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6893,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6954,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7015,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7076,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7137,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7198,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7259,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7320,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7381,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7442,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7503,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:50</t>
+          <t>2026-09-29 01:39:38</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7564,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7625,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7686,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7747,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7808,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7869,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7930,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7991,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8052,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8113,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8174,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8235,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8296,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8357,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8418,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:52</t>
+          <t>2026-09-29 01:39:39</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8479,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8540,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8601,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8662,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8723,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8784,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8845,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8906,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8967,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9028,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9089,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9150,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9211,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9272,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9333,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:53</t>
+          <t>2026-09-29 01:39:40</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9394,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9455,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9516,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9577,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9638,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:54</t>
+          <t>2026-09-29 01:39:41</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9699,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9760,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9821,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9882,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9943,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10004,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10065,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10126,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10187,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10248,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10309,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10370,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10431,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10492,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10553,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10614,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10675,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10736,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10797,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10858,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10919,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10980,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11041,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11102,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11163,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11224,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11285,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11346,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11407,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11468,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11529,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11590,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11651,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11712,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11773,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11834,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11895,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11956,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12017,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12078,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12139,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12200,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12261,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12322,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12383,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12444,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12505,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12566,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12627,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12688,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12749,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12810,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12871,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12932,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12993,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13054,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13115,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13176,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13237,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13298,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13359,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13420,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13481,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13542,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13603,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13664,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13725,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13786,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13847,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13908,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13969,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14030,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14091,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14152,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14213,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14274,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14335,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14396,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14457,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14518,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14579,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14640,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14701,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14762,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14823,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14884,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14945,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -15006,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15067,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15128,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15189,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15250,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15311,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15372,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15433,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15494,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15555,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15616,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15677,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15738,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15799,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15860,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15921,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15982,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16043,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16104,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16165,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16226,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16287,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16348,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16409,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16470,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16531,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16592,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16653,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16714,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16775,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16836,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16897,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16958,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17019,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17080,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:18</t>
+          <t>2026-09-29 01:40:08</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17141,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17202,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17263,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17324,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17385,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17446,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17507,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17568,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17629,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17690,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17751,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17812,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17873,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17934,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17995,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:19</t>
+          <t>2026-09-29 01:40:09</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18056,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18117,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18178,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18239,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18300,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18361,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18422,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18483,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18544,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18605,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18666,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18727,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18788,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18849,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18910,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:20</t>
+          <t>2026-09-29 01:40:10</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18971,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19032,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19093,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19154,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19215,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:22</t>
+          <t>2026-09-29 01:40:11</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19276,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19337,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19398,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19459,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19520,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19581,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19642,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19703,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19764,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19825,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19886,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19947,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -20008,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20069,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20130,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:27</t>
+          <t>2026-09-29 01:40:18</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20191,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20252,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20313,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20374,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20435,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20496,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20557,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20618,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20679,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20740,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20801,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20862,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20923,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20984,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21045,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:28</t>
+          <t>2026-09-29 01:40:19</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21106,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21167,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21228,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21289,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21350,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21411,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21472,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21533,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21594,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21655,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21716,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21777,7 +21747,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:29</t>
+          <t>2026-09-29 01:40:20</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21838,7 +21808,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:34</t>
+          <t>2026-09-29 01:40:25</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21901,7 +21871,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:34</t>
+          <t>2026-09-29 01:40:25</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21964,7 +21934,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:34</t>
+          <t>2026-09-29 01:40:25</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22027,7 +21997,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22090,7 +22060,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22153,7 +22123,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22216,7 +22186,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22279,7 +22249,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22342,7 +22312,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:35</t>
+          <t>2026-09-29 01:40:27</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22405,7 +22375,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22468,7 +22438,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22531,7 +22501,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22594,7 +22564,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22657,7 +22627,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22720,7 +22690,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22783,7 +22753,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:37</t>
+          <t>2026-09-29 01:40:28</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22846,7 +22816,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:38</t>
+          <t>2026-09-29 01:40:29</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22909,7 +22879,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:38</t>
+          <t>2026-09-29 01:40:29</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22972,7 +22942,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -23033,7 +23003,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23094,7 +23064,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23155,7 +23125,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23216,7 +23186,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23277,7 +23247,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23338,7 +23308,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23399,7 +23369,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23460,7 +23430,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23521,7 +23491,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23582,7 +23552,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23643,7 +23613,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23704,7 +23674,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23765,7 +23735,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23826,7 +23796,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23887,7 +23857,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23948,7 +23918,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -24009,7 +23979,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24070,7 +24040,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24131,7 +24101,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24192,7 +24162,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24253,7 +24223,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24314,7 +24284,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24375,7 +24345,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24436,7 +24406,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24497,7 +24467,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24558,7 +24528,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24619,7 +24589,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24680,7 +24650,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24741,7 +24711,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24802,7 +24772,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24863,7 +24833,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24924,7 +24894,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24985,7 +24955,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25046,7 +25016,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25107,7 +25077,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25168,7 +25138,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25229,7 +25199,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25290,7 +25260,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25351,7 +25321,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25412,7 +25382,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25473,7 +25443,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25534,7 +25504,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25595,7 +25565,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25656,7 +25626,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25717,7 +25687,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25778,7 +25748,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25839,7 +25809,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25900,7 +25870,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25961,7 +25931,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -26022,7 +25992,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26083,7 +26053,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26144,7 +26114,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26205,7 +26175,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26266,7 +26236,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26327,7 +26297,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26388,7 +26358,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26449,7 +26419,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26510,7 +26480,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26571,7 +26541,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26632,7 +26602,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26693,7 +26663,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26754,7 +26724,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26815,7 +26785,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26876,7 +26846,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26937,7 +26907,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26998,7 +26968,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27059,7 +27029,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27120,7 +27090,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27181,7 +27151,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27242,7 +27212,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27303,7 +27273,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27364,7 +27334,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27425,7 +27395,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27486,7 +27456,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27547,7 +27517,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27608,7 +27578,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27669,7 +27639,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27730,7 +27700,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27791,7 +27761,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27852,7 +27822,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27913,7 +27883,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27974,7 +27944,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28035,7 +28005,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28096,7 +28066,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28157,7 +28127,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28218,7 +28188,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28279,7 +28249,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28340,7 +28310,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28401,7 +28371,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28462,7 +28432,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28523,7 +28493,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28584,7 +28554,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28645,7 +28615,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28706,7 +28676,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28767,7 +28737,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28828,7 +28798,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28889,7 +28859,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28950,7 +28920,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -29011,7 +28981,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29072,7 +29042,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29133,7 +29103,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29194,7 +29164,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29255,7 +29225,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29316,7 +29286,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29377,7 +29347,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29438,7 +29408,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29499,7 +29469,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29560,7 +29530,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29621,7 +29591,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29682,7 +29652,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29743,7 +29713,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29804,7 +29774,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29865,7 +29835,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29926,7 +29896,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29987,7 +29957,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30048,7 +30018,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30109,7 +30079,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30170,7 +30140,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30231,7 +30201,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30292,7 +30262,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30353,7 +30323,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30414,7 +30384,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30475,7 +30445,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30536,7 +30506,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30597,7 +30567,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30658,7 +30628,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30719,7 +30689,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30780,7 +30750,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30841,7 +30811,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30902,7 +30872,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30963,7 +30933,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -31024,7 +30994,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31085,7 +31055,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31146,7 +31116,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31207,7 +31177,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31268,7 +31238,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31329,7 +31299,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31390,7 +31360,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31451,7 +31421,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31512,7 +31482,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31573,7 +31543,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31634,7 +31604,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31695,7 +31665,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31756,7 +31726,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31817,7 +31787,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31878,7 +31848,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31939,7 +31909,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -32000,7 +31970,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32061,7 +32031,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32122,7 +32092,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32183,7 +32153,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32244,7 +32214,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32305,7 +32275,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32366,7 +32336,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32427,7 +32397,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32488,7 +32458,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32549,7 +32519,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32610,7 +32580,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32671,7 +32641,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32732,7 +32702,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32793,7 +32763,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32854,7 +32824,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:12</t>
+          <t>2026-09-29 01:41:05</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32915,7 +32885,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32976,7 +32946,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33037,7 +33007,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33098,7 +33068,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33159,7 +33129,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33220,7 +33190,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33281,7 +33251,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33342,7 +33312,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33403,7 +33373,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33464,7 +33434,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33525,7 +33495,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33586,7 +33556,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33647,7 +33617,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33708,7 +33678,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33769,7 +33739,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:14</t>
+          <t>2026-09-29 01:41:06</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33830,7 +33800,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33891,7 +33861,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33952,7 +33922,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -34013,7 +33983,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34074,7 +34044,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34135,7 +34105,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34196,7 +34166,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34257,7 +34227,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34318,7 +34288,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34379,7 +34349,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -34440,7 +34410,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -34501,7 +34471,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -34562,7 +34532,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -34623,7 +34593,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -34684,7 +34654,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:15</t>
+          <t>2026-09-29 01:41:08</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
